--- a/human_validation/judge/kor/judge_D007_S005_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S005_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B86"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,440 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 그게, 요즘 제가 제 모습이 아닌 것 같아서 왔어요. 말수도 많이 줄고, 사람들이랑 얘기도 잘 안 하게 되고, 대부분 그냥 좀 멍한 느낌이에요. 직장에서 청소 구역 도는 것도 마치 무거운 카트를 언덕 위로 미는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 상태가 얼마나 오래되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 꽤 오래됐어요... 한 1년 5개월 정도 된 것 같아요. 예전에 살던 아파트랑 익숙했던 동네를 떠난 뒤부터 본격적으로 쌓이기 시작한 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 예전에 즐기시던 활동들에서 여전히 즐거움을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 사실 별로요. 예전엔 토요일마다 낚시하러 가는 것도 기대되고, 커피 마시면서 십자말풀이 하는 것도 좋았어요. 직장에서도 젊은 친구들한테 바닥 왁스 벗기는 요령 같은 걸 알려주곤 했고요. 근데 지금은 그냥 그런 것들을 손도 안 대고 놔두게 돼요. 더 이상 저한테 뭘 주는 게 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 아침에 기분이 더 안 좋으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 아침에 더 안 좋다고 느낀 적은 없는 것 같아요. 그냥 하루 종일 계속 있는 느낌에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 대부분의 시간 동안 불안하거나 초조하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 대부분이라고 할 수 있을지는 모르겠어요. 가끔 불편한 느낌이 들긴 하는데, 그런 걸 딱히 기록해 놓지는 않았어요. 제가 가장 크게 느끼는 건 그게 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이런 상태가 시작된 이후로 체중에 변화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 그런 것 같아요. 요즘 많이 안 먹게 돼요. 대부분 음식이 아무 맛도 안 나서 끼니를 거르거나 퇴근하고 크래커 몇 개 먹는 게 다예요. 작업 바지도 예전보다 헐렁해졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 스스로를 다치게 하고 싶다는 생각을 하신 적 있으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 딱히 뭔가 큰 계획이 있는 건 아니에요. 근데... 아침에 일어날 때 그냥 아예 안 깨어나는 게 더 편하지 않을까 하는 생각이 드는 날이 많아요. 그게 좀 무섭게 느껴져서, 이건 말씀드려야겠다고 생각했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 예전보다 움직임이 느려지셨거나 빨라지셨다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 더 빨라졌다고 느낀 적은 없어요. 어떤 날은 조금 느려진 것 같기도 한데, 확실하게 말씀드리긴 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 상태가 시작된 이후로 이상한 생각이 들거나, 다른 사람들은 듣지 못하는 목소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네... 뭔가 들리긴 해요. 야간에 대걸레질하고 있을 때, 가끔 남자 목소리가 제 이름을 부르거나 제가 한 군데를 빼먹었다고 말하는 걸 들어요. 계단 쪽에 서 있는 것처럼 아주 또렷하게 들리는데, 돌아보면 아무도 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 말씀하신 그 목소리 말고, 실제로 존재하지 않는 뭔가를 보거나 듣거나 느끼신 다른 경험이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 그 외엔 딱히 없어요. 주로 직장에서 야간에 들리는 그 목소리예요—남자가 제 이름을 부르거나 한 군데 빼먹었다고 말하는 것 같은. 계단 쪽에 있는 것처럼 가깝게 들리는데, 확인해 보면 아무도 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 그 목소리가 어떤 식으로든 본인의 생각이나 행동을 조종하고 있다고 생각해 보신 적 있으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 그 목소리가 정확히 저를 조종한다고는 생각 안 해요. 그보다는 새 건물주랑 건물에 있는 몇 사람이 복도 카메라 같은 걸로 저를 감시하고 있다는 생각이 계속 떠나지 않아요... 저에 대해 뭔가 메시지를 주고받고 있는 것 같기도 하고요. 사람들은 그 카메라가 그냥 현관용이라고 하는데, 저는 그렇게 느껴지지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 밖에 나가 계실 때 사람들이 본인에 대해 이야기하거나 지켜보고 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네... 주로 제가 사는 건물 주변에서요. 새 건물주랑 거기 있는 몇 사람이 복도 카메라로 저를 지켜보거나, 저에 대해 서로 이야기하고 있다는 생각이 계속 떠나지 않아요. 사람들은 그 카메라가 그냥 현관용이라고 하는데, 그래도 저를 계속 감시하고 있는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] TV에서 보거나 듣는 것, 신문에서 읽는 것들이 어떤 식으로든 본인과 관련이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] TV나 신문은 딱히 아니에요. 그보다는 제가 사는 건물에 관한 거예요... 새 건물주랑 거기 몇 사람이 복도 카메라로 저를 감시하거나 저에 대해 메시지를 주고받고 있다는 생각이 계속 들어요. 사람들은 카메라가 그냥 현관용이라고 하는데, 그래도 여전히 저와 관련이 있는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 다른 사람들에게 일어나는 일이나 사건들이 어떤 식으로든 본인과 관련이 있거나 본인을 향한 메시지라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 다른 사람들에게 일어나는 일이랑은 딱히 상관없어요. 그보다는... 제가 사는 건물에서, 새 건물주랑 몇 사람이 그 복도 카메라로 저를 지켜보거나, 저에 대해 서로 메시지를 주고받는다는 생각이 계속 들어요. 사람들이 카메라는 그냥 현관용이라고 하는 건 아는데, 그래도 여전히 저를 감시하고 있는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 본인을 감시하거나 본인에 대해 이야기한다고 생각하시는 사람들이 본인에 대해 뭔가 음모를 꾸미고 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] '음모'라고까지 말할 수 있을지는 모르겠어요. 그보다는 새 건물주랑 아마 건물의 몇 사람이 복도 카메라로 저를 감시하고, 저에 대해 이야기하거나 메시지를 주고받고 있다는 느낌이 들어요. 사람들은 카메라가 그냥 현관용이라고 하는데, 그래도 계속 그 생각에서 벗어나지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 본인을 감시하고 있다고 생각하시는 사람들이 본인에게 해를 끼치고 싶어 한다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 저를 해치고 싶어 한다고까지는 생각 안 해요. 그보다는 복도 카메라로 저를 감시하고, 저에 대해 이야기하거나 메시지를 주고받는 것 같은 느낌이에요. 사람들이 카메라는 그냥 현관용이라고 하는 건 아는데, 그래도 여전히 저랑 관련이 있다는 생각에서 벗어나지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 다른 사람들과 이야기할 때 본인의 생각을 표현하거나 요점을 전달하는 게 힘드신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 네, 가끔요. 직장에서 감독관이 제가 몇 층까지 청소했는지 같은 간단한 걸 물어보면, 대답을 시작하다가 어느새 예전 버스 노선이나 텃밭, 교회 지하실 얘기를 하고 있어요. 그러고 있는 제 목소리가 들리는데, 실제 질문으로 돌아가지 못하고 있는 느낌이에요. 답답해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 본인을 감시하고 있다고 생각하시는 사람들이 실제로 본인에게 해를 끼치거나 어떤 식으로든 삶을 통제할 수 있다고 믿으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 제 삶을 통제할 수 있다고는 생각 안 해요. 해를 끼치는 거는... 잘 모르겠어요. 그보다는 새 건물주랑 건물의 몇 사람이 복도 카메라로 저를 감시하고 저에 대한 메시지를 주고받는다는 생각이 계속 들어요. 사람들은 계속 카메라가 그냥 현관용이라고 하는데, 그래도 어떤 식으로든 저랑 관련이 있다는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 질문에 답을 하다가 다른 주제로 새어버린다고 하신 게 정확히 어떤 의미인지 좀 더 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 그러니까... 감독관이 '몇 층까지 끝냈어요?' 하고 물으면, 대답을 시작하긴 하는데 그러다 생각이 다른 데로 새요. 예전 버스 노선이나 텃밭, 아니면 교회 지하실 이야기를 하기 시작하고, 정작 그가 물어본 것에는 제대로 답을 못 하고 있어요.
+가끔은 제가 그러고 있는 걸 스스로 듣기도 해요. 요점으로 돌아가지 못하고 있다는 걸 아는데, 다시 끌어오기가 힘들어요. 질문이 간단한 거였는데도 그러니까 답답해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 다른 사람들과 대화할 때 주제를 유지하는 게 힘드신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 네. 가끔 그래요. 아까 말씀드렸듯이, 감독관이 제가 몇 층까지 끝냈는지 같은 간단한 걸 물어보면 대답을 시작하는데, 그러다 예전 버스 노선이나 텃밭, 교회 지하실 얘기로 흘러가요. 제대로 된 답으로 돌아가지 못하고 있다는 걸 알면서도, 계속 그 주제에 머물러 있기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (우울형) (D007)
 인구통계: 성별 남성 / 나이 59 / 직업상태 janitor or building cleaner / 최종학력 대학 재학
@@ -575,507 +1000,50 @@
 증상 지속 기간: 1 year and 5 months
 추가 요건: psychotic_symptoms and depressive_episode occur concurrently, depressive_episode is present for the majority of the total duration of the active and residual portions of the illness (Criterion C), delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode (Criterion B)
 주호소 증상 코드: S023
-배경 서술: 스티븐이 오랫동안 임대해 살던 아파트 건물이 매각되면서, 그는 수년간 교회, 텃밭, 무료급식소 이용, 출퇴근 경로가 안정적으로 자리 잡았던 동네를 떠나 이사할 수밖에 없었다. 이후 1년 5개월에 걸쳐 이런 변화는 점차 임상적으로 의미 있는 수준이 되어, 지속적이고 고정된 믿음과 뚜렷한 환각 유사 경험이 우울 삽화와 함께 나타났고, 조리 없는 의사소통과 이상한 행동이 동료와 이웃들 눈에 점점 더 자주 띄었다. 그는 낚시와 목공, 십자말풀이 루틴, 후배 관리인 지도에서 물러났고, 식욕과 기력을 잃었으며, 죄책감과 자신의 삶이 끝나가고 있다는 생각에 짓눌렸다. 한편 정신증적 증상은 기분이 덜 우울했던 시기에도 함께 나타났다. 시설 관리 감독관이 반복되는 업무 지장을 문서화하고, 스티븐 스스로도 더 이상 건물 관리 업무를 제대로 해낼 수 없다는 것을 인정한 뒤에야 그는 회사의 지원 프로그램을 통해 도움을 구했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 그게, 요즘 제가 제 모습이 아닌 것 같아서 왔어요. 말수도 많이 줄고, 사람들이랑 얘기도 잘 안 하게 되고, 대부분 그냥 좀 멍한 느낌이에요. 직장에서 청소 구역 도는 것도 마치 무거운 카트를 언덕 위로 미는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 상태가 얼마나 오래되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 꽤 오래됐어요... 한 1년 5개월 정도 된 것 같아요. 예전에 살던 아파트랑 익숙했던 동네를 떠난 뒤부터 본격적으로 쌓이기 시작한 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 예전에 즐기시던 활동들에서 여전히 즐거움을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 사실 별로요. 예전엔 토요일마다 낚시하러 가는 것도 기대되고, 커피 마시면서 십자말풀이 하는 것도 좋았어요. 직장에서도 젊은 친구들한테 바닥 왁스 벗기는 요령 같은 걸 알려주곤 했고요. 근데 지금은 그냥 그런 것들을 손도 안 대고 놔두게 돼요. 더 이상 저한테 뭘 주는 게 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 아침에 기분이 더 안 좋으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 아침에 더 안 좋다고 느낀 적은 없는 것 같아요. 그냥 하루 종일 계속 있는 느낌에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 대부분의 시간 동안 불안하거나 초조하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 대부분이라고 할 수 있을지는 모르겠어요. 가끔 불편한 느낌이 들긴 하는데, 그런 걸 딱히 기록해 놓지는 않았어요. 제가 가장 크게 느끼는 건 그게 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이런 상태가 시작된 이후로 체중에 변화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 그런 것 같아요. 요즘 많이 안 먹게 돼요. 대부분 음식이 아무 맛도 안 나서 끼니를 거르거나 퇴근하고 크래커 몇 개 먹는 게 다예요. 작업 바지도 예전보다 헐렁해졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 스스로를 다치게 하고 싶다는 생각을 하신 적 있으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 딱히 뭔가 큰 계획이 있는 건 아니에요. 근데... 아침에 일어날 때 그냥 아예 안 깨어나는 게 더 편하지 않을까 하는 생각이 드는 날이 많아요. 그게 좀 무섭게 느껴져서, 이건 말씀드려야겠다고 생각했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 예전보다 움직임이 느려지셨거나 빨라지셨다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 더 빨라졌다고 느낀 적은 없어요. 어떤 날은 조금 느려진 것 같기도 한데, 확실하게 말씀드리긴 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 상태가 시작된 이후로 이상한 생각이 들거나, 다른 사람들은 듣지 못하는 목소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네... 뭔가 들리긴 해요. 야간에 대걸레질하고 있을 때, 가끔 남자 목소리가 제 이름을 부르거나 제가 한 군데를 빼먹었다고 말하는 걸 들어요. 계단 쪽에 서 있는 것처럼 아주 또렷하게 들리는데, 돌아보면 아무도 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 말씀하신 그 목소리 말고, 실제로 존재하지 않는 뭔가를 보거나 듣거나 느끼신 다른 경험이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 그 외엔 딱히 없어요. 주로 직장에서 야간에 들리는 그 목소리예요—남자가 제 이름을 부르거나 한 군데 빼먹었다고 말하는 것 같은. 계단 쪽에 있는 것처럼 가깝게 들리는데, 확인해 보면 아무도 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 그 목소리가 어떤 식으로든 본인의 생각이나 행동을 조종하고 있다고 생각해 보신 적 있으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 그 목소리가 정확히 저를 조종한다고는 생각 안 해요. 그보다는 새 건물주랑 건물에 있는 몇 사람이 복도 카메라 같은 걸로 저를 감시하고 있다는 생각이 계속 떠나지 않아요... 저에 대해 뭔가 메시지를 주고받고 있는 것 같기도 하고요. 사람들은 그 카메라가 그냥 현관용이라고 하는데, 저는 그렇게 느껴지지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 밖에 나가 계실 때 사람들이 본인에 대해 이야기하거나 지켜보고 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네... 주로 제가 사는 건물 주변에서요. 새 건물주랑 거기 있는 몇 사람이 복도 카메라로 저를 지켜보거나, 저에 대해 서로 이야기하고 있다는 생각이 계속 떠나지 않아요. 사람들은 그 카메라가 그냥 현관용이라고 하는데, 그래도 저를 계속 감시하고 있는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] TV에서 보거나 듣는 것, 신문에서 읽는 것들이 어떤 식으로든 본인과 관련이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] TV나 신문은 딱히 아니에요. 그보다는 제가 사는 건물에 관한 거예요... 새 건물주랑 거기 몇 사람이 복도 카메라로 저를 감시하거나 저에 대해 메시지를 주고받고 있다는 생각이 계속 들어요. 사람들은 카메라가 그냥 현관용이라고 하는데, 그래도 여전히 저와 관련이 있는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 다른 사람들에게 일어나는 일이나 사건들이 어떤 식으로든 본인과 관련이 있거나 본인을 향한 메시지라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 다른 사람들에게 일어나는 일이랑은 딱히 상관없어요. 그보다는... 제가 사는 건물에서, 새 건물주랑 몇 사람이 그 복도 카메라로 저를 지켜보거나, 저에 대해 서로 메시지를 주고받는다는 생각이 계속 들어요. 사람들이 카메라는 그냥 현관용이라고 하는 건 아는데, 그래도 여전히 저를 감시하고 있는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 본인을 감시하거나 본인에 대해 이야기한다고 생각하시는 사람들이 본인에 대해 뭔가 음모를 꾸미고 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] '음모'라고까지 말할 수 있을지는 모르겠어요. 그보다는 새 건물주랑 아마 건물의 몇 사람이 복도 카메라로 저를 감시하고, 저에 대해 이야기하거나 메시지를 주고받고 있다는 느낌이 들어요. 사람들은 카메라가 그냥 현관용이라고 하는데, 그래도 계속 그 생각에서 벗어나지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 본인을 감시하고 있다고 생각하시는 사람들이 본인에게 해를 끼치고 싶어 한다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 저를 해치고 싶어 한다고까지는 생각 안 해요. 그보다는 복도 카메라로 저를 감시하고, 저에 대해 이야기하거나 메시지를 주고받는 것 같은 느낌이에요. 사람들이 카메라는 그냥 현관용이라고 하는 건 아는데, 그래도 여전히 저랑 관련이 있다는 생각에서 벗어나지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 다른 사람들과 이야기할 때 본인의 생각을 표현하거나 요점을 전달하는 게 힘드신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 네, 가끔요. 직장에서 감독관이 제가 몇 층까지 청소했는지 같은 간단한 걸 물어보면, 대답을 시작하다가 어느새 예전 버스 노선이나 텃밭, 교회 지하실 얘기를 하고 있어요. 그러고 있는 제 목소리가 들리는데, 실제 질문으로 돌아가지 못하고 있는 느낌이에요. 답답해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 본인을 감시하고 있다고 생각하시는 사람들이 실제로 본인에게 해를 끼치거나 어떤 식으로든 삶을 통제할 수 있다고 믿으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 제 삶을 통제할 수 있다고는 생각 안 해요. 해를 끼치는 거는... 잘 모르겠어요. 그보다는 새 건물주랑 건물의 몇 사람이 복도 카메라로 저를 감시하고 저에 대한 메시지를 주고받는다는 생각이 계속 들어요. 사람들은 계속 카메라가 그냥 현관용이라고 하는데, 그래도 어떤 식으로든 저랑 관련이 있다는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 질문에 답을 하다가 다른 주제로 새어버린다고 하신 게 정확히 어떤 의미인지 좀 더 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 그러니까... 감독관이 '몇 층까지 끝냈어요?' 하고 물으면, 대답을 시작하긴 하는데 그러다 생각이 다른 데로 새요. 예전 버스 노선이나 텃밭, 아니면 교회 지하실 이야기를 하기 시작하고, 정작 그가 물어본 것에는 제대로 답을 못 하고 있어요.
-가끔은 제가 그러고 있는 걸 스스로 듣기도 해요. 요점으로 돌아가지 못하고 있다는 걸 아는데, 다시 끌어오기가 힘들어요. 질문이 간단한 거였는데도 그러니까 답답해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 다른 사람들과 대화할 때 주제를 유지하는 게 힘드신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 네. 가끔 그래요. 아까 말씀드렸듯이, 감독관이 제가 몇 층까지 끝냈는지 같은 간단한 걸 물어보면 대답을 시작하는데, 그러다 예전 버스 노선이나 텃밭, 교회 지하실 얘기로 흘러가요. 제대로 된 답으로 돌아가지 못하고 있다는 걸 알면서도, 계속 그 주제에 머물러 있기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 스티븐이 오랫동안 임대해 살던 아파트 건물이 매각되면서, 그는 수년간 교회, 텃밭, 무료급식소 이용, 출퇴근 경로가 안정적으로 자리 잡았던 동네를 떠나 이사할 수밖에 없었다. 이후 1년 5개월에 걸쳐 이런 변화는 점차 임상적으로 의미 있는 수준이 되어, 지속적이고 고정된 믿음과 뚜렷한 환각 유사 경험이 우울 삽화와 함께 나타났고, 조리 없는 의사소통과 이상한 행동이 동료와 이웃들 눈에 점점 더 자주 띄었다. 그는 낚시와 목공, 십자말풀이 루틴, 후배 관리인 지도에서 물러났고, 식욕과 기력을 잃었으며, 죄책감과 자신의 삶이 끝나가고 있다는 생각에 짓눌렸다. 한편 정신증적 증상은 기분이 덜 우울했던 시기에도 함께 나타났다. 시설 관리 감독관이 반복되는 업무 지장을 문서화하고, 스티븐 스스로도 더 이상 건물 관리 업무를 제대로 해낼 수 없다는 것을 인정한 뒤에야 그는 회사의 지원 프로그램을 통해 도움을 구했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S021 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 조현병 (D005, ICD: F20.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=4, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
-  누락: 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 조현병 (D005, ICD: F20.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=4, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+  - 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S005_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S005_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -986,6 +986,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1039,11 +1044,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S005_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S005_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2015</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.2015</v>
+        <v>0.1803</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3947</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
